--- a/processo_2/synthetic_proposals/PROPOSTA_016/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_016/ficha_pontuacao.xlsx
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,17 +749,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3062-3185</t>
+          <t>4837-8403</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -824,7 +824,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1083,7 +1083,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1668,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
@@ -1851,7 +1851,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1866,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
